--- a/business_forms/028_hair_extension_agreement_form_studio_37--business_forms.xlsx
+++ b/business_forms/028_hair_extension_agreement_form_studio_37--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -684,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dark_brown</t>
+          <t>ginger</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dark Brown</t>
+          <t>Ginger</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ginger</t>
+          <t>ash_brown</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ginger</t>
+          <t>Ash Brown</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ash_brown</t>
+          <t>ash_blonde</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ash Brown</t>
+          <t>Ash Blonde</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ash_blonde</t>
+          <t>honey_golden</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ash Blonde</t>
+          <t>Honey Golden</t>
         </is>
       </c>
     </row>
@@ -870,29 +870,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>honey_golden</t>
+          <t>platinum_blonde</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Honey Golden</t>
+          <t>Platinum Blonde</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hair_type_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>platinum_blonde</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Platinum Blonde</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>credit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Credit</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>credit</t>
+          <t>debit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>debit</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -955,29 +955,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>paypal</t>
+          <t>cash_app</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Cash App</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_terms_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>cash_app</t>
+          <t>30_days</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cash App</t>
+          <t>30 days</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30_days</t>
+          <t>45_days</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>45 days</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>45_days</t>
+          <t>60_days</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>45 days</t>
+          <t>60 days</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>60_days</t>
+          <t>90_days</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>60 days</t>
+          <t>90 days</t>
         </is>
       </c>
     </row>
@@ -1040,27 +1040,10 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90_days</t>
+          <t>120_days</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>90 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>payment_terms_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>120_days</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
         <is>
           <t>120 days</t>
         </is>
